--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 23:21</t>
+    <t xml:space="preserve">2026-08-17 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:28</t>
+    <t xml:space="preserve">2026-08-17 20:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 20:40</t>
+    <t xml:space="preserve">2026-09-06 20:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
